--- a/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Common-Kestrel.xlsx
+++ b/wildlife/reports/United-Kingdom/trend/Abingdon/Birds/Common-Kestrel.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
